--- a/data/trans_dic/P39A1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>68,97; 76,35</t>
+          <t>69,01; 76,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>66,21; 72,19</t>
+          <t>65,83; 71,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68,62; 73,34</t>
+          <t>68,44; 73,33</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,17; 90,12</t>
+          <t>75,31; 90,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,02; 77,0</t>
+          <t>72,54; 77,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,85; 85,38</t>
+          <t>74,81; 86,08</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,08; 68,15</t>
+          <t>58,25; 67,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,67; 87,17</t>
+          <t>60,53; 87,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,54; 79,74</t>
+          <t>61,61; 80,58</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>67,08; 73,7</t>
+          <t>66,96; 73,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,16; 66,95</t>
+          <t>47,99; 67,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,11; 68,83</t>
+          <t>54,84; 68,89</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,24; 80,19</t>
+          <t>70,44; 79,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>65,0; 74,24</t>
+          <t>64,76; 74,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,27; 74,97</t>
+          <t>68,32; 75,12</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar, mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>386752; 428155</t>
+          <t>386983; 427691</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>389155; 424341</t>
+          <t>386979; 422629</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>788118; 842327</t>
+          <t>786076; 842203</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>842159; 1009624</t>
+          <t>843687; 1010768</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>634180; 678023</t>
+          <t>638811; 681059</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1497658; 1708339</t>
+          <t>1496917; 1722337</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>391135; 451214</t>
+          <t>385669; 447131</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>513936; 738378</t>
+          <t>512697; 738124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>928710; 1203372</t>
+          <t>929780; 1216025</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>572368; 628860</t>
+          <t>571355; 627857</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>465620; 660969</t>
+          <t>473773; 662147</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1051112; 1266931</t>
+          <t>1009361; 1268000</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2245141; 2563337</t>
+          <t>2251465; 2526047</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2146870; 2451928</t>
+          <t>2138889; 2451416</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4437255; 4872637</t>
+          <t>4440457; 4882168</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A1_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A1_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,01; 76,27</t>
+          <t>68,85; 76,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>65,83; 71,9</t>
+          <t>66,61; 72,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68,44; 73,33</t>
+          <t>68,93; 73,54</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>75,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,31; 90,22</t>
+          <t>73,34; 79,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>72,54; 77,34</t>
+          <t>72,28; 76,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74,81; 86,08</t>
+          <t>73,62; 77,3</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>62,03%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,25; 67,54</t>
+          <t>59,1; 66,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,53; 87,14</t>
+          <t>58,18; 64,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,61; 80,58</t>
+          <t>59,36; 64,61</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>68,04%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,96; 73,58</t>
+          <t>67,0; 73,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,99; 67,07</t>
+          <t>63,58; 68,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>54,84; 68,89</t>
+          <t>65,79; 69,92</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,44; 79,03</t>
+          <t>69,08; 72,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,76; 74,22</t>
+          <t>66,72; 69,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,32; 75,12</t>
+          <t>68,31; 70,5</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>407709</t>
+          <t>438489</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>407036</t>
+          <t>440283</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>814746</t>
+          <t>878772</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>386983; 427691</t>
+          <t>414307; 458945</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>386979; 422629</t>
+          <t>421705; 460473</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>786076; 842203</t>
+          <t>851142; 908105</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>913494</t>
+          <t>731347</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>658339</t>
+          <t>733988</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1571833</t>
+          <t>1465335</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>843687; 1010768</t>
+          <t>701646; 757667</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>638811; 681059</t>
+          <t>710406; 755648</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1496917; 1722337</t>
+          <t>1427922; 1499409</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>419629</t>
+          <t>469738</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>600091</t>
+          <t>458194</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1019720</t>
+          <t>927931</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>385669; 447131</t>
+          <t>441760; 500560</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>512697; 738124</t>
+          <t>435501; 482334</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>929780; 1216025</t>
+          <t>887960; 966532</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>600163</t>
+          <t>634727</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>605691</t>
+          <t>660211</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1205853</t>
+          <t>1294938</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>571355; 627857</t>
+          <t>605678; 663353</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>473773; 662147</t>
+          <t>635367; 686711</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1009361; 1268000</t>
+          <t>1252128; 1330801</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2340996</t>
+          <t>2274301</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2271157</t>
+          <t>2292676</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4612153</t>
+          <t>4566977</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2251465; 2526047</t>
+          <t>2217596; 2329826</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2138889; 2451416</t>
+          <t>2244329; 2337865</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4440457; 4882168</t>
+          <t>4490424; 4634367</t>
         </is>
       </c>
     </row>
